--- a/output/pdf_financials_xlsx/SGO.xlsx
+++ b/output/pdf_financials_xlsx/SGO.xlsx
@@ -1303,25 +1303,25 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.141581</v>
+        <v>-0.141581</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.17352</v>
+        <v>-0.17352</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.282003</v>
+        <v>-0.282003</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.927834</v>
+        <v>-0.892296</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.470608</v>
+        <v>-0.506146</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.285539</v>
+        <v>-0.285539</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.620051</v>
+        <v>-0.620051</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.947944</v>
@@ -1619,25 +1619,25 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.141581</v>
+        <v>-0.141581</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.17352</v>
+        <v>-0.17352</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.282003</v>
+        <v>-0.282003</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.910065</v>
+        <v>-0.910065</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.488377</v>
+        <v>-0.488377</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.285539</v>
+        <v>-0.285539</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.620051</v>
+        <v>-0.620051</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.947944</v>
@@ -1802,25 +1802,25 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.141581</v>
+        <v>-0.141581</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.17352</v>
+        <v>-0.17352</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.282003</v>
+        <v>-0.282003</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.910065</v>
+        <v>-0.910065</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.488377</v>
+        <v>-0.488377</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.285539</v>
+        <v>-0.285539</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.620051</v>
+        <v>-0.620051</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-0.947944</v>
@@ -1985,19 +1985,19 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>2.359683</v>
+        <v>-2.359683</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2.892</v>
+        <v>-2.892</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>2.563664</v>
+        <v>-2.563664</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>13.000929</v>
+        <v>-13.000929</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>24.41885</v>
+        <v>-24.41885</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-12.40102</v>
+        <v>12.40102</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>23.6986</v>
@@ -2050,25 +2050,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.141581</v>
+        <v>-0.141581</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.17352</v>
+        <v>-0.17352</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.282003</v>
+        <v>-0.282003</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.927834</v>
+        <v>-0.892296</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.470608</v>
+        <v>-0.506146</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.285539</v>
+        <v>-0.285539</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.620051</v>
+        <v>-0.620051</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.947944</v>
@@ -2172,25 +2172,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.141581</v>
+        <v>-0.141581</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.17352</v>
+        <v>-0.17352</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.282003</v>
+        <v>-0.282003</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.928518</v>
+        <v>-0.891612</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.470608</v>
+        <v>-0.506146</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.285539</v>
+        <v>-0.285539</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.620051</v>
+        <v>-0.620051</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.947944</v>
@@ -2330,25 +2330,25 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1.915105503786238</v>
+        <v>-1.991379542214691</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3.77575391833543</v>
+        <v>-3.510647125532949</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -6128,49 +6128,49 @@
         <v>0.06201</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.218796</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.394851</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.37092</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.45131</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.118582</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.236302</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.214112</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.140489</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.462819</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.891019</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.005737</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.005737</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>2.005737</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>3.124757</v>
       </c>
     </row>
     <row r="93">
@@ -10480,7 +10480,11 @@
           <t>Share-based payment reserve 10</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -12814,7 +12818,11 @@
           <t>Share-based payment reserve 10 2,005,737</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -14296,7 +14304,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -15042,7 +15054,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -15786,7 +15802,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -18230,7 +18250,11 @@
           <t>Share-based payment reserve 10</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -22980,7 +23004,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -23622,7 +23650,11 @@
           <t>Share-based payment reserve (note 9)</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -24482,7 +24514,11 @@
           <t>Reserves (note 11)</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -25784,7 +25820,11 @@
           <t>Reserves (note 13) 218,796</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -57238,10 +57278,10 @@
         </is>
       </c>
       <c r="K464" s="5" t="n">
-        <v>0.620051</v>
+        <v>-0.620051</v>
       </c>
       <c r="L464" s="5" t="n">
-        <v>0.947944</v>
+        <v>-0.947944</v>
       </c>
       <c r="M464" t="inlineStr">
         <is>
@@ -58289,13 +58329,13 @@
         </is>
       </c>
       <c r="H474" s="5" t="n">
-        <v>0.910065</v>
+        <v>-0.910065</v>
       </c>
       <c r="I474" s="5" t="n">
-        <v>0.488377</v>
+        <v>-0.488377</v>
       </c>
       <c r="J474" s="5" t="n">
-        <v>0.285539</v>
+        <v>-0.285539</v>
       </c>
       <c r="K474" t="inlineStr">
         <is>
@@ -60098,10 +60138,10 @@
         </is>
       </c>
       <c r="G491" s="5" t="n">
-        <v>0.282003</v>
+        <v>-0.282003</v>
       </c>
       <c r="H491" s="5" t="n">
-        <v>0.910065</v>
+        <v>-0.910065</v>
       </c>
       <c r="I491" t="inlineStr">
         <is>
@@ -60942,13 +60982,13 @@
         </is>
       </c>
       <c r="E499" s="5" t="n">
-        <v>0.141581</v>
+        <v>-0.141581</v>
       </c>
       <c r="F499" s="5" t="n">
-        <v>0.17352</v>
+        <v>-0.17352</v>
       </c>
       <c r="G499" s="5" t="n">
-        <v>0.186755</v>
+        <v>-0.186755</v>
       </c>
       <c r="H499" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SGO.xlsx
+++ b/output/pdf_financials_xlsx/SGO.xlsx
@@ -1059,55 +1059,55 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005195</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.012059</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003335</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00648</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008928</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008746</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004323</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.00342</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>3.6e-05</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.002429</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.078934</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000847</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.000142</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.002928</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.002948</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.001471</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>4e-05</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>0</v>
@@ -2050,55 +2050,55 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.141581</v>
+        <v>-0.136386</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.17352</v>
+        <v>-0.161461</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.282003</v>
+        <v>-0.278668</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.892296</v>
+        <v>-0.885816</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.506146</v>
+        <v>-0.497218</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.285539</v>
+        <v>-0.276793</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.620051</v>
+        <v>-0.6157280000000001</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.947944</v>
+        <v>-0.951364</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.443385</v>
+        <v>-0.443421</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.316947</v>
+        <v>1.314518</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.479504</v>
+        <v>-2.558438</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.75641</v>
+        <v>-1.757257</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-5.648579</v>
+        <v>-5.648721</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-5.873982</v>
+        <v>-5.87691</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-6.907158</v>
+        <v>-6.910106</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-3.81153</v>
+        <v>-3.813001</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-1.287334</v>
+        <v>-1.287374</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>-5.408962</v>
@@ -2172,55 +2172,55 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.141581</v>
+        <v>-0.136386</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.17352</v>
+        <v>-0.161461</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.282003</v>
+        <v>-0.278668</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.891612</v>
+        <v>-0.885132</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.506146</v>
+        <v>-0.497218</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.285539</v>
+        <v>-0.276793</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.620051</v>
+        <v>-0.6157280000000001</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.947944</v>
+        <v>-0.951364</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.443385</v>
+        <v>-0.443421</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.316947</v>
+        <v>1.314518</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.479504</v>
+        <v>-2.558438</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.75641</v>
+        <v>-1.757257</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-5.648579</v>
+        <v>-5.648721</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-5.869913</v>
+        <v>-5.872841</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-6.85833</v>
+        <v>-6.861278</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.721628</v>
+        <v>-3.723099</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.224771</v>
+        <v>-1.224811</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>-5.345466</v>
@@ -2537,16 +2537,16 @@
         <v>1.761106</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.087545</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.000877</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.214084</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>4.562725</v>
       </c>
     </row>
     <row r="35">
@@ -2659,16 +2659,16 @@
         <v>1.761106</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.087545</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.000877</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.214084</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>4.562725</v>
       </c>
     </row>
     <row r="37">
@@ -3391,16 +3391,16 @@
         <v>0.149147</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.546347</v>
+        <v>0.458802</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.14915</v>
+        <v>0.148273</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.408635</v>
+        <v>1.194551</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>5.36116</v>
+        <v>0.798435</v>
       </c>
     </row>
     <row r="49">
@@ -8066,19 +8066,19 @@
         <v>0</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.004412</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.054445</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.106821</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-0.074695</v>
       </c>
     </row>
     <row r="125">
@@ -8127,19 +8127,19 @@
         <v>0</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.004412</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.054445</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.106821</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-0.074695</v>
       </c>
     </row>
     <row r="126">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -29226,7 +29226,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -30928,7 +30932,11 @@
           <t>Lease payment</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -42312,7 +42320,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -42410,7 +42418,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -45118,7 +45126,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -47972,7 +47980,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -51932,7 +51940,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -52038,7 +52046,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -54800,7 +54808,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -56822,7 +56830,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -59590,7 +59598,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -60872,7 +60880,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E498" s="5" t="n">

--- a/output/pdf_financials_xlsx/SGO.xlsx
+++ b/output/pdf_financials_xlsx/SGO.xlsx
@@ -1336,10 +1336,10 @@
         <v>-2.479504</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-1.75641</v>
+        <v>-1.03114</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-5.648579</v>
+        <v>-5.642646</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>-5.873982</v>
@@ -1397,10 +1397,10 @@
         <v>-0</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.72527</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.005933</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>-0</v>
@@ -2083,10 +2083,10 @@
         <v>-2.558438</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.757257</v>
+        <v>-1.031987</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-5.648721</v>
+        <v>-5.642788</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-5.87691</v>
@@ -2205,10 +2205,10 @@
         <v>-2.558438</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.757257</v>
+        <v>-1.031987</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-5.648721</v>
+        <v>-5.642788</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-5.872841</v>
@@ -2363,10 +2363,10 @@
         <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0</v>
+        <v>-70.33671470411389</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.1051457064646621</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>-0</v>
@@ -4561,43 +4561,43 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.031607</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.028307</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.0205</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.171747</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.04272</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.160054</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.124829</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.435333</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>0</v>
@@ -6523,7 +6523,7 @@
         <v>-0.443385</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>-0.443385</v>
+        <v>0.591677</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>-2.479504</v>
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001523</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000133</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>-0.001072</v>
@@ -6923,10 +6923,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.207767</v>
+        <v>-0.20929</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.056973</v>
+        <v>0.05684</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.271525</v>
@@ -28712,7 +28712,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -35356,7 +35360,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -37482,7 +37490,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -39716,7 +39728,11 @@
           <t>GST/HST receivable</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -40688,7 +40704,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E306" s="5" t="n">
         <v>-0.001523</v>
       </c>
@@ -47130,7 +47150,11 @@
           <t>Income tax recovery 13</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E368" t="inlineStr">
         <is>
           <t>-</t>
@@ -48192,7 +48216,11 @@
           <t>Income tax recovery 12</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -58210,7 +58238,11 @@
           <t>Deferred income tax recovery (note 10)</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
           <t>-</t>
